--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540A151B-AE34-47AA-989B-2C9029564DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CEA2D5-95DC-4EB1-9E2B-37157B95D93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$6</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>OM</t>
   </si>
@@ -31,7 +28,112 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Ordem pendente!</t>
+    <t>5201029</t>
+  </si>
+  <si>
+    <t>5202759</t>
+  </si>
+  <si>
+    <t>5202761</t>
+  </si>
+  <si>
+    <t>5202815</t>
+  </si>
+  <si>
+    <t>5202904</t>
+  </si>
+  <si>
+    <t>5201333</t>
+  </si>
+  <si>
+    <t>5201688</t>
+  </si>
+  <si>
+    <t>5201738</t>
+  </si>
+  <si>
+    <t>5201830</t>
+  </si>
+  <si>
+    <t>5201879</t>
+  </si>
+  <si>
+    <t>5201904</t>
+  </si>
+  <si>
+    <t>5202024</t>
+  </si>
+  <si>
+    <t>5202077</t>
+  </si>
+  <si>
+    <t>5202393</t>
+  </si>
+  <si>
+    <t>5202469</t>
+  </si>
+  <si>
+    <t>5202762</t>
+  </si>
+  <si>
+    <t>5202867</t>
+  </si>
+  <si>
+    <t>685601397903</t>
+  </si>
+  <si>
+    <t>685601390008</t>
+  </si>
+  <si>
+    <t>685601410835</t>
+  </si>
+  <si>
+    <t>685601401087</t>
+  </si>
+  <si>
+    <t>685601407137</t>
+  </si>
+  <si>
+    <t>685601397950</t>
+  </si>
+  <si>
+    <t>685601402323</t>
+  </si>
+  <si>
+    <t>685601402466</t>
+  </si>
+  <si>
+    <t>685601403348</t>
+  </si>
+  <si>
+    <t>685601413543</t>
+  </si>
+  <si>
+    <t>685601404377</t>
+  </si>
+  <si>
+    <t>85601405522</t>
+  </si>
+  <si>
+    <t>685601407615</t>
+  </si>
+  <si>
+    <t>685601407616</t>
+  </si>
+  <si>
+    <t>685601407641</t>
+  </si>
+  <si>
+    <t>685601408796</t>
+  </si>
+  <si>
+    <t>685601398085</t>
+  </si>
+  <si>
+    <t>685601409171</t>
+  </si>
+  <si>
+    <t>685601409255</t>
   </si>
 </sst>
 </file>
@@ -87,15 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -400,11 +499,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -416,43 +515,243 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>685601400376</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>685601403633</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>685601407005</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>685601407007</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>685601400030</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>2</v>
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>5201859</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>5201889</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>5201890</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>5202155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>5202586</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>5202104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>685601385222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>685601397945</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>685601414742</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>685601404101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>685601404102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>685601414149</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CEA2D5-95DC-4EB1-9E2B-37157B95D93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642E11A3-DB26-4D35-939C-B0AA06E59614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>OM</t>
   </si>
@@ -28,112 +28,85 @@
     <t>Status</t>
   </si>
   <si>
-    <t>5201029</t>
-  </si>
-  <si>
-    <t>5202759</t>
-  </si>
-  <si>
-    <t>5202761</t>
-  </si>
-  <si>
-    <t>5202815</t>
-  </si>
-  <si>
-    <t>5202904</t>
-  </si>
-  <si>
-    <t>5201333</t>
-  </si>
-  <si>
-    <t>5201688</t>
-  </si>
-  <si>
-    <t>5201738</t>
-  </si>
-  <si>
-    <t>5201830</t>
-  </si>
-  <si>
-    <t>5201879</t>
+    <t>5201851</t>
+  </si>
+  <si>
+    <t>5202214</t>
+  </si>
+  <si>
+    <t>5202880</t>
+  </si>
+  <si>
+    <t>5202180</t>
+  </si>
+  <si>
+    <t>5203155</t>
+  </si>
+  <si>
+    <t>5202587</t>
+  </si>
+  <si>
+    <t>5203054</t>
+  </si>
+  <si>
+    <t>5202196</t>
   </si>
   <si>
     <t>5201904</t>
   </si>
   <si>
-    <t>5202024</t>
-  </si>
-  <si>
-    <t>5202077</t>
-  </si>
-  <si>
-    <t>5202393</t>
-  </si>
-  <si>
-    <t>5202469</t>
-  </si>
-  <si>
-    <t>5202762</t>
-  </si>
-  <si>
-    <t>5202867</t>
-  </si>
-  <si>
-    <t>685601397903</t>
-  </si>
-  <si>
-    <t>685601390008</t>
-  </si>
-  <si>
-    <t>685601410835</t>
-  </si>
-  <si>
-    <t>685601401087</t>
-  </si>
-  <si>
-    <t>685601407137</t>
-  </si>
-  <si>
-    <t>685601397950</t>
-  </si>
-  <si>
-    <t>685601402323</t>
-  </si>
-  <si>
-    <t>685601402466</t>
-  </si>
-  <si>
-    <t>685601403348</t>
-  </si>
-  <si>
-    <t>685601413543</t>
-  </si>
-  <si>
-    <t>685601404377</t>
-  </si>
-  <si>
-    <t>85601405522</t>
-  </si>
-  <si>
-    <t>685601407615</t>
-  </si>
-  <si>
-    <t>685601407616</t>
-  </si>
-  <si>
-    <t>685601407641</t>
-  </si>
-  <si>
-    <t>685601408796</t>
-  </si>
-  <si>
-    <t>685601398085</t>
-  </si>
-  <si>
-    <t>685601409171</t>
-  </si>
-  <si>
-    <t>685601409255</t>
+    <t>5201906</t>
+  </si>
+  <si>
+    <t>5203092</t>
+  </si>
+  <si>
+    <t>5202972</t>
+  </si>
+  <si>
+    <t>5201799</t>
+  </si>
+  <si>
+    <t>5202340</t>
+  </si>
+  <si>
+    <t>5202728</t>
+  </si>
+  <si>
+    <t>5202714</t>
+  </si>
+  <si>
+    <t>5203012</t>
+  </si>
+  <si>
+    <t>685601417804</t>
+  </si>
+  <si>
+    <t>685601407997</t>
+  </si>
+  <si>
+    <t>685601408143</t>
+  </si>
+  <si>
+    <t>685601412380</t>
+  </si>
+  <si>
+    <t>685601417162</t>
+  </si>
+  <si>
+    <t>685601417806</t>
+  </si>
+  <si>
+    <t>685601403281</t>
+  </si>
+  <si>
+    <t>685601411449</t>
+  </si>
+  <si>
+    <t>685601403947</t>
+  </si>
+  <si>
+    <t>685601410831</t>
   </si>
 </sst>
 </file>
@@ -189,13 +162,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -649,111 +619,6 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>5201859</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>5201889</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>5201890</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>5202155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>5202586</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>5202104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>685601385222</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>685601397945</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>685601414742</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>685601404101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>685601404102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>685601414149</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -1,135 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642E11A3-DB26-4D35-939C-B0AA06E59614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>OM</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>5201851</t>
-  </si>
-  <si>
-    <t>5202214</t>
-  </si>
-  <si>
-    <t>5202880</t>
-  </si>
-  <si>
-    <t>5202180</t>
-  </si>
-  <si>
-    <t>5203155</t>
-  </si>
-  <si>
-    <t>5202587</t>
-  </si>
-  <si>
-    <t>5203054</t>
-  </si>
-  <si>
-    <t>5202196</t>
-  </si>
-  <si>
-    <t>5201904</t>
-  </si>
-  <si>
-    <t>5201906</t>
-  </si>
-  <si>
-    <t>5203092</t>
-  </si>
-  <si>
-    <t>5202972</t>
-  </si>
-  <si>
-    <t>5201799</t>
-  </si>
-  <si>
-    <t>5202340</t>
-  </si>
-  <si>
-    <t>5202728</t>
-  </si>
-  <si>
-    <t>5202714</t>
-  </si>
-  <si>
-    <t>5203012</t>
-  </si>
-  <si>
-    <t>685601417804</t>
-  </si>
-  <si>
-    <t>685601407997</t>
-  </si>
-  <si>
-    <t>685601408143</t>
-  </si>
-  <si>
-    <t>685601412380</t>
-  </si>
-  <si>
-    <t>685601417162</t>
-  </si>
-  <si>
-    <t>685601417806</t>
-  </si>
-  <si>
-    <t>685601403281</t>
-  </si>
-  <si>
-    <t>685601411449</t>
-  </si>
-  <si>
-    <t>685601403947</t>
-  </si>
-  <si>
-    <t>685601410831</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -144,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -468,156 +420,241 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OM</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5201851</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5202214</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5202880</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5202180</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5203155</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5202587</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5203054</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5202196</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5201904</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5201906</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5203092</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5202972</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5201799</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5202340</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5202728</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5202714</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5203012</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>685601417804</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>685601407997</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>685601408143</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>685601412380</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>685601417162</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>685601417806</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>685601403281</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>685601411449</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>685601403947</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>685601410831</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB707205-C7F0-44BC-A5DE-74C7F48963EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718987DE-09AA-4D0E-AB54-D55B0FA7120F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>OM</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Encerrado!</t>
+    <t>Encerrar na transação Z22I101</t>
   </si>
 </sst>
 </file>
@@ -84,11 +84,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -391,10 +392,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -406,242 +408,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>5202597</v>
+      <c r="A2" s="2">
+        <v>685601421518</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5202521</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>5202588</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5203348</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5201430</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5201937</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5201544</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5202807</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>5201854</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>5203315</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>5203237</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>685601361310</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>685601420342</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>685601418894</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>685601408213</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>685601417868</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>685601410367</v>
-      </c>
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>685601407628</v>
-      </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>685601411011</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>685601410718</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>685601403343</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>685601400030</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>685601403876</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>685601409317</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>685601410137</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>685601408214</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>685601408217</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>685601389094</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>685601415784</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>685601413512</v>
-      </c>
-      <c r="B31" t="s">
         <v>2</v>
       </c>
     </row>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718987DE-09AA-4D0E-AB54-D55B0FA7120F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D161BDDB-2D01-4B3B-B46E-3A443DA763E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>OM</t>
   </si>
@@ -28,7 +28,67 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Encerrar na transação Z22I101</t>
+    <t>5203871</t>
+  </si>
+  <si>
+    <t>5202393</t>
+  </si>
+  <si>
+    <t>5203655</t>
+  </si>
+  <si>
+    <t>5198523</t>
+  </si>
+  <si>
+    <t>5203287</t>
+  </si>
+  <si>
+    <t>5200467</t>
+  </si>
+  <si>
+    <t>5203828</t>
+  </si>
+  <si>
+    <t>5203013</t>
+  </si>
+  <si>
+    <t>5202719</t>
+  </si>
+  <si>
+    <t>5195967</t>
+  </si>
+  <si>
+    <t>5203191</t>
+  </si>
+  <si>
+    <t>5203909</t>
+  </si>
+  <si>
+    <t>5203915</t>
+  </si>
+  <si>
+    <t>5202090</t>
+  </si>
+  <si>
+    <t>685601400634</t>
+  </si>
+  <si>
+    <t>685601418024</t>
+  </si>
+  <si>
+    <t>685601415845</t>
+  </si>
+  <si>
+    <t>685601410576</t>
+  </si>
+  <si>
+    <t>685601422072</t>
+  </si>
+  <si>
+    <t>685601413995</t>
+  </si>
+  <si>
+    <t>685601403343</t>
   </si>
 </sst>
 </file>
@@ -84,12 +144,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,11 +451,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -408,11 +466,108 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>685601421518</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D161BDDB-2D01-4B3B-B46E-3A443DA763E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652601A5-402D-4DE2-B8EB-3E1BE85BFF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>OM</t>
   </si>
@@ -28,67 +28,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>5203871</t>
-  </si>
-  <si>
-    <t>5202393</t>
-  </si>
-  <si>
-    <t>5203655</t>
-  </si>
-  <si>
-    <t>5198523</t>
-  </si>
-  <si>
-    <t>5203287</t>
-  </si>
-  <si>
-    <t>5200467</t>
-  </si>
-  <si>
-    <t>5203828</t>
-  </si>
-  <si>
-    <t>5203013</t>
-  </si>
-  <si>
-    <t>5202719</t>
-  </si>
-  <si>
-    <t>5195967</t>
-  </si>
-  <si>
-    <t>5203191</t>
-  </si>
-  <si>
-    <t>5203909</t>
-  </si>
-  <si>
-    <t>5203915</t>
-  </si>
-  <si>
-    <t>5202090</t>
-  </si>
-  <si>
-    <t>685601400634</t>
-  </si>
-  <si>
-    <t>685601418024</t>
-  </si>
-  <si>
-    <t>685601415845</t>
-  </si>
-  <si>
-    <t>685601410576</t>
-  </si>
-  <si>
-    <t>685601422072</t>
-  </si>
-  <si>
-    <t>685601413995</t>
-  </si>
-  <si>
-    <t>685601403343</t>
+    <t>Ordem pendente!</t>
   </si>
 </sst>
 </file>
@@ -144,10 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,10 +394,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -466,108 +410,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2">
+        <v>685601413995</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-OMs.xlsx
+++ b/08 - Excels/Open-OMs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652601A5-402D-4DE2-B8EB-3E1BE85BFF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2B5AFE-06A9-4770-8629-3C6E8271792D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>OM</t>
   </si>
@@ -28,7 +28,52 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Ordem pendente!</t>
+    <t>5204073</t>
+  </si>
+  <si>
+    <t>5203228</t>
+  </si>
+  <si>
+    <t>5203993</t>
+  </si>
+  <si>
+    <t>5201959</t>
+  </si>
+  <si>
+    <t>5202074</t>
+  </si>
+  <si>
+    <t>5203401</t>
+  </si>
+  <si>
+    <t>5203580</t>
+  </si>
+  <si>
+    <t>685601423689</t>
+  </si>
+  <si>
+    <t>685601416637</t>
+  </si>
+  <si>
+    <t>685601422071</t>
+  </si>
+  <si>
+    <t>685601422586</t>
+  </si>
+  <si>
+    <t>685601417668</t>
+  </si>
+  <si>
+    <t>685601418417</t>
+  </si>
+  <si>
+    <t>685601407004</t>
+  </si>
+  <si>
+    <t>685601423704</t>
+  </si>
+  <si>
+    <t>685601424008</t>
   </si>
 </sst>
 </file>
@@ -84,13 +129,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,11 +436,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -410,11 +452,83 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>685601413995</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
